--- a/docs/测试用例.xlsx
+++ b/docs/测试用例.xlsx
@@ -11765,7 +11765,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-509151；执行结果：通过</t>
+          <t>前端联调测试商品-035629；执行结果：通过</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-509151；执行结果：通过</t>
+          <t>前端联调测试商品-035629；执行结果：通过</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-509151；执行结果：通过</t>
+          <t>前端联调测试商品-035629；执行结果：通过</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">	 | 确认完成 | 取消订单；执行结果：通过</t>
+          <t>已完成 | 	 | —；执行结果：通过</t>
         </is>
       </c>
       <c r="J213" s="3" t="inlineStr">

--- a/docs/测试用例.xlsx
+++ b/docs/测试用例.xlsx
@@ -565,7 +565,7 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. 使用「匿名（不登录）」身份发起 POST 请求：/api/auth/register
-2. 请求体（application/json）：{   "username": "stu1789780379534",   "password": "123456",   "nickname": "接口测试新同学",   "phone": "13800138000",   "email": "stu@campus.com",   "school": "南昌职业大学" }
+2. 请求体（application/json）：{   "username": "stu1789785214233",   "password": "123456",   "nickname": "接口测试新同学",   "phone": "13800138000",   "email": "stu@campus.com",   "school": "南昌职业大学" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 184 ms；断言 5/5 通过；返回信息：注册成功</t>
+          <t>HTTP 200，业务码 200，耗时 97 ms；断言 5/5 通过；返回信息：注册成功</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -624,7 +624,7 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. 使用「匿名（不登录）」身份发起 POST 请求：/api/auth/register
-2. 请求体（application/json）：{   "username": "stu1789780379534",   "password": "123456",   "nickname": "重复注册" }
+2. 请求体（application/json）：{   "username": "stu1789785214233",   "password": "123456",   "nickname": "重复注册" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40904，耗时 11 ms；断言 3/3 通过；返回信息：用户名已存在</t>
+          <t>HTTP 409，业务码 40904，耗时 12 ms；断言 3/3 通过；返回信息：用户名已存在</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 10 ms；断言 3/3 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 3/3 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 5 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 5 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 90 ms；断言 5/5 通过；返回信息：登录成功</t>
+          <t>HTTP 200，业务码 200，耗时 63 ms；断言 5/5 通过；返回信息：登录成功</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 62 ms；断言 3/3 通过；返回信息：登录成功</t>
+          <t>HTTP 200，业务码 200，耗时 60 ms；断言 3/3 通过；返回信息：登录成功</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 63 ms；断言 3/3 通过；返回信息：登录成功</t>
+          <t>HTTP 200，业务码 200，耗时 60 ms；断言 3/3 通过；返回信息：登录成功</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 62 ms；断言 3/3 通过；返回信息：登录成功</t>
+          <t>HTTP 200，业务码 200，耗时 59 ms；断言 3/3 通过；返回信息：登录成功</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. 使用「匿名（不登录）」身份发起 POST 请求：/api/auth/login
-2. 请求体（application/json）：{   "username": "stu1789780379534",   "password": "123456" }
+2. 请求体（application/json）：{   "username": "stu1789785214233",   "password": "123456" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 65 ms；断言 2/2 通过；返回信息：登录成功</t>
+          <t>HTTP 200，业务码 200，耗时 61 ms；断言 2/2 通过；返回信息：登录成功</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40102，耗时 58 ms；断言 3/3 通过；返回信息：用户名或密码错误</t>
+          <t>HTTP 401，业务码 40102，耗时 57 ms；断言 3/3 通过；返回信息：用户名或密码错误</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40102，耗时 7 ms；断言 2/2 通过；返回信息：用户名或密码错误</t>
+          <t>HTTP 401，业务码 40102，耗时 6 ms；断言 2/2 通过；返回信息：用户名或密码错误</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 5 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 5 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 4 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 12 ms；断言 2/2 通过；返回信息：登录状态无效或已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 3 ms；断言 2/2 通过；返回信息：登录状态无效或已过期，请重新登录</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 20 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 17 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 67 ms；断言 3/3 通过；返回信息：原密码不正确</t>
+          <t>HTTP 400，业务码 40001，耗时 66 ms；断言 3/3 通过；返回信息：原密码不正确</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 62 ms；断言 2/2 通过；返回信息：新密码不能与原密码相同</t>
+          <t>HTTP 400，业务码 40001，耗时 63 ms；断言 2/2 通过；返回信息：新密码不能与原密码相同</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 10 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：退出成功</t>
+          <t>HTTP 200，业务码 200，耗时 7 ms；断言 3/3 通过；返回信息：退出成功</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 8 ms；断言 5/5 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 5/5 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 5 ms；断言 2/2 通过；返回信息：用户不存在</t>
+          <t>HTTP 404，业务码 40401，耗时 6 ms；断言 2/2 通过；返回信息：用户不存在</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'id': Failed to convert value of type 'java.lang.String</t>
+          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'id': Failed to convert value of type 'java.lang.String</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 73 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 21 ms；断言 3/3 通过；返回信息：资料更新成功</t>
+          <t>HTTP 200，业务码 200，耗时 16 ms；断言 3/3 通过；返回信息：资料更新成功</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 7 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 5 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>HTTP 405，业务码 40500，耗时 5 ms；断言 2/2 通过；返回信息：Request method 'POST' is not supported</t>
+          <t>HTTP 405，业务码 40500，耗时 3 ms；断言 2/2 通过；返回信息：Request method 'POST' is not supported</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 5/5 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 7 ms；断言 5/5 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 16 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 10 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 7 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 5 ms；断言 3/3 通过；返回信息：页码必须大于等于 1</t>
+          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 3/3 通过；返回信息：页码必须大于等于 1</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：每页条数必须在 1-100 之间</t>
+          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：每页条数必须在 1-100 之间</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：每页条数必须在 1-100 之间</t>
+          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：每页条数必须在 1-100 之间</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 4 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'page': Failed to convert value of type 'java.lang.Stri</t>
+          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'page': Failed to convert value of type 'java.lang.Stri</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 3/3 通过；返回信息：最低价格不能大于最高价格</t>
+          <t>HTTP 400，业务码 40001，耗时 5 ms；断言 3/3 通过；返回信息：最低价格不能大于最高价格</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 10 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 6 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 16 ms；断言 6/6 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 6/6 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 6 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
+          <t>HTTP 404，业务码 40401，耗时 4 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 3 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'id': Failed to convert value of type 'java.lang.String</t>
+          <t>HTTP 400，业务码 40001，耗时 2 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'id': Failed to convert value of type 'java.lang.String</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 31 ms；断言 3/3 通过；返回信息：发布成功</t>
+          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：发布成功</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 14 ms；断言 3/3 通过；返回信息：发布成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：发布成功</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 14 ms；断言 3/3 通过；返回信息：发布成功</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：发布成功</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 14 ms；断言 3/3 通过；返回信息：发布成功</t>
+          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：发布成功</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 10 ms；断言 3/3 通过；返回信息：商品分类不存在</t>
+          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 3/3 通过；返回信息：商品分类不存在</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/products/21
+          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/products/22
 2. 请求体（application/json）：{   "title": "越权修改",   "price": 1,   "categoryId": 1,   "conditionLevel": "全新" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 11 ms；断言 3/3 通过；返回信息：只能编辑自己发布的商品</t>
+          <t>HTTP 403，业务码 40301，耗时 10 ms；断言 3/3 通过；返回信息：只能编辑自己发布的商品</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/products/21
+          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/products/22
 2. 请求体（application/json）：{   "title": "接口测试商品-已修改",   "description": "修改后的描述",   "price": 88.8,   "originalPrice": 199.0,   "categoryId": 2,   "conditionLevel": "八成新",   "tradePlace": "三号宿舍楼下",   "imageUrls": [     "/seed/p02.png"   ] }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 21 ms；断言 3/3 通过；返回信息：修改成功</t>
+          <t>HTTP 200，业务码 200，耗时 17 ms；断言 3/3 通过；返回信息：修改成功</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 9 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
+          <t>HTTP 404，业务码 40401，耗时 7 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/21/status
+          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/22/status
 2. 请求体（application/json）：{   "status": "OFF_SHELF" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/21/status
+          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/22/status
 2. 请求体（application/json）：{   "status": "OFF_SHELF" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40902，耗时 9 ms；断言 2/2 通过；返回信息：只有在售商品才能下架</t>
+          <t>HTTP 409，业务码 40902，耗时 7 ms；断言 2/2 通过；返回信息：只有在售商品才能下架</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/21/status
+          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/22/status
 2. 请求体（application/json）：{   "status": "ON_SALE" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/21/status
+          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/22/status
 2. 请求体（application/json）：{   "status": "SOLD" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/21/status
+          <t>1. 使用「非法 token」身份发起 PATCH 请求：/api/products/22/status
 2. 请求体（application/json）：{   "status": "OFF_SHELF" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 11 ms；断言 2/2 通过；返回信息：只能操作自己发布的商品</t>
+          <t>HTTP 403，业务码 40301，耗时 9 ms；断言 2/2 通过；返回信息：只能操作自己发布的商品</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 17 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 3 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 4 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 22 ms；断言 3/3 通过；返回信息：上传成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：上传成功</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40002，耗时 9 ms；断言 3/3 通过；返回信息：文件类型不支持，仅允许上传 jpg/jpeg/png</t>
+          <t>HTTP 400，业务码 40002，耗时 8 ms；断言 3/3 通过；返回信息：文件类型不支持，仅允许上传 jpg/jpeg/png</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40003，耗时 38 ms；断言 2/2 通过；返回信息：文件大小超过限制（单个文件最大 5MB）</t>
+          <t>HTTP 400，业务码 40003，耗时 35 ms；断言 2/2 通过；返回信息：文件大小超过限制（单个文件最大 5MB）</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 8 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 7 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/favorites/21
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/favorites/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/favorites/21
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/favorites/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：你已经收藏过该商品</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：你已经收藏过该商品</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 9 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
+          <t>HTTP 404，业务码 40401，耗时 7 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'productId': Failed to convert value of type 'java.lang</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：请求参数不合法：Method parameter 'productId': Failed to convert value of type 'java.lang</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 GET 请求：/api/favorites/21/status
+          <t>1. 使用「非法 token」身份发起 GET 请求：/api/favorites/22/status
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 4 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 3 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 DELETE 请求：/api/favorites/21
+          <t>1. 使用「非法 token」身份发起 DELETE 请求：/api/favorites/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 19 ms；断言 3/3 通过；返回信息：取消收藏成功</t>
+          <t>HTTP 200，业务码 200，耗时 18 ms；断言 3/3 通过；返回信息：取消收藏成功</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 DELETE 请求：/api/favorites/21
+          <t>1. 使用「非法 token」身份发起 DELETE 请求：/api/favorites/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：你尚未收藏该商品</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：你尚未收藏该商品</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 GET 请求：/api/favorites/21/status
+          <t>1. 使用「非法 token」身份发起 GET 请求：/api/favorites/22/status
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 7 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -6185,7 +6185,7 @@
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "21",   "remark": "接口测试下单：今晚 7 点图书馆一楼交易" }
+2. 请求体（application/json）：{   "productId": "22",   "remark": "接口测试下单：今晚 7 点图书馆一楼交易" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 29 ms；断言 6/6 通过；返回信息：下单成功，等待卖家确认</t>
+          <t>HTTP 200，业务码 200，耗时 17 ms；断言 6/6 通过；返回信息：下单成功，等待卖家确认</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/21
+          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "21",   "remark": "重复提交" }
+2. 请求体（application/json）：{   "productId": "22",   "remark": "重复提交" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40901，耗时 10 ms；断言 3/3 通过；返回信息：你已对该商品下过订单，请勿重复提交</t>
+          <t>HTTP 409，业务码 40901，耗时 8 ms；断言 3/3 通过；返回信息：你已对该商品下过订单，请勿重复提交</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -6361,7 +6361,7 @@
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "21" }
+2. 请求体（application/json）：{   "productId": "22" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40903，耗时 9 ms；断言 3/3 通过；返回信息：不能购买自己发布的商品</t>
+          <t>HTTP 409，业务码 40903，耗时 8 ms；断言 3/3 通过；返回信息：不能购买自己发布的商品</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
@@ -6420,7 +6420,7 @@
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "21" }
+2. 请求体（application/json）：{   "productId": "22" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 9 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
+          <t>HTTP 404，业务码 40401，耗时 8 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 9 ms；断言 2/2 通过；返回信息：参数校验失败</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：参数校验失败</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -6597,7 +6597,7 @@
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "22",   "remark": "测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测
+2. 请求体（application/json）：{   "productId": "23",   "remark": "测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测测
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 4 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 3 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 2/2 通过；返回信息：角色参数只支持：buyer、seller、all</t>
+          <t>HTTP 400，业务码 40001，耗时 6 ms；断言 2/2 通过；返回信息：角色参数只支持：buyer、seller、all</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401，业务码 40101，耗时 5 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
+          <t>HTTP 401，业务码 40101，耗时 4 ms；断言 2/2 通过；返回信息：未登录或登录已过期，请重新登录</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/3
+          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/4
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/3
+          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/4
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 7 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/3
+          <t>1. 使用「非法 token」身份发起 GET 请求：/api/orders/4
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 7 ms；断言 2/2 通过；返回信息：订单不存在</t>
+          <t>HTTP 404，业务码 40401，耗时 6 ms；断言 2/2 通过；返回信息：订单不存在</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/confirm
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/confirm
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 8 ms；断言 2/2 通过；返回信息：只有卖家可以确认订单</t>
+          <t>HTTP 403，业务码 40301，耗时 7 ms；断言 2/2 通过；返回信息：只有卖家可以确认订单</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/confirm
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/confirm
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 18 ms；断言 4/4 通过；返回信息：已确认订单，请尽快完成交易</t>
+          <t>HTTP 200，业务码 200，耗时 12 ms；断言 4/4 通过；返回信息：已确认订单，请尽快完成交易</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/confirm
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/confirm
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/finish
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/finish
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 9 ms；断言 2/2 通过；返回信息：只有买家可以确认完成</t>
+          <t>HTTP 403，业务码 40301，耗时 6 ms；断言 2/2 通过；返回信息：只有买家可以确认完成</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/finish
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/finish
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 20 ms；断言 4/4 通过；返回信息：交易已完成</t>
+          <t>HTTP 200，业务码 200，耗时 15 ms；断言 4/4 通过；返回信息：交易已完成</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/21
+          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/22
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/3/cancel
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/cancel
 2. 请求体（application/json）：{   "reason": "完成后想取消" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40902，耗时 12 ms；断言 2/2 通过；返回信息：只有待确认或交易中的订单才能取消（当前状态：已完成）</t>
+          <t>HTTP 409，业务码 40902，耗时 10 ms；断言 2/2 通过；返回信息：只有待确认或交易中的订单才能取消（当前状态：已完成）</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
@@ -7702,7 +7702,7 @@
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders
-2. 请求体（application/json）：{   "productId": "22",   "remark": "取消流程测试" }
+2. 请求体（application/json）：{   "productId": "23",   "remark": "取消流程测试" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 21 ms；断言 3/3 通过；返回信息：下单成功，等待卖家确认</t>
+          <t>HTTP 200，业务码 200，耗时 16 ms；断言 3/3 通过；返回信息：下单成功，等待卖家确认</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/cancel
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/5/cancel
 2. 请求体（application/json）：{   "reason": "临时不想要了" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 16 ms；断言 4/4 通过；返回信息：订单已取消</t>
+          <t>HTTP 200，业务码 200，耗时 15 ms；断言 4/4 通过；返回信息：订单已取消</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/22
+          <t>1. 使用「匿名（不登录）」身份发起 GET 请求：/api/products/23
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 18 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/4/cancel
+          <t>1. 使用「非法 token」身份发起 POST 请求：/api/orders/5/cancel
 2. 请求体（application/json）：{   "reason": "再次取消" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 9 ms；断言 2/2 通过；返回信息：订单不存在</t>
+          <t>HTTP 404，业务码 40401，耗时 8 ms；断言 2/2 通过；返回信息：订单不存在</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 6 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 9 ms；断言 3/3 通过；返回信息：只能操作自己的消息</t>
+          <t>HTTP 403，业务码 40301，耗时 7 ms；断言 3/3 通过；返回信息：只能操作自己的消息</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 8 ms；断言 2/2 通过；返回信息：消息不存在</t>
+          <t>HTTP 404，业务码 40401，耗时 7 ms；断言 2/2 通过；返回信息：消息不存在</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：已全部标记为已读</t>
+          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：已全部标记为已读</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 6 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 18 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404，业务码 40401，耗时 8 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
+          <t>HTTP 404，业务码 40401，耗时 7 ms；断言 2/2 通过；返回信息：商品不存在或已删除</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
@@ -8923,68 +8923,68 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
+          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/admin/products/24/off-shelf
+2. 查看响应状态码、业务返回码与响应字段</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200，业务码 200；并满足 3 条断言：HTTP 状态码 200、业务返回码 200、返回成功</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：已强制下架</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>执行方式：newman 批量执行；对应集合请求「144 强制下架-管理员下架商品成功」</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>TC-IF-145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>08-管理端</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>145 强制下架-普通用户无权操作</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>后端服务已启动（http://localhost:8080），数据库处于初始数据状态；Postman 环境变量已就绪（token、商品 ID、订单 ID 由前置用例自动写入）</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
           <t>1. 使用「非法 token」身份发起 PUT 请求：/api/admin/products/23/off-shelf
 2. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 200，业务码 200；并满足 3 条断言：HTTP 状态码 200、业务返回码 200、返回成功</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：已强制下架</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>执行方式：newman 批量执行；对应集合请求「144 强制下架-管理员下架商品成功」</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>TC-IF-145</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>08-管理端</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>145 强制下架-普通用户无权操作</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>后端服务已启动（http://localhost:8080），数据库处于初始数据状态；Postman 环境变量已就绪（token、商品 ID、订单 ID 由前置用例自动写入）</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>1. 使用「非法 token」身份发起 PUT 请求：/api/admin/products/22/off-shelf
-2. 查看响应状态码、业务返回码与响应字段</t>
-        </is>
-      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>HTTP 403，业务码 40303；并满足 2 条断言：HTTP 状态码 403、业务返回码 40303</t>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 19 ms；断言 4/4 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 12 ms；断言 4/4 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 12 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40301，耗时 13 ms；断言 3/3 通过；返回信息：不能修改自己的账号状态</t>
+          <t>HTTP 403，业务码 40301，耗时 14 ms；断言 3/3 通过；返回信息：不能修改自己的账号状态</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 15 ms；断言 3/3 通过；返回信息：用户状态已更新</t>
+          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：用户状态已更新</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40302，耗时 5 ms；断言 3/3 通过；返回信息：账号已被禁用，请联系管理员</t>
+          <t>HTTP 403，业务码 40302，耗时 4 ms；断言 3/3 通过；返回信息：账号已被禁用，请联系管理员</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
@@ -9332,7 +9332,7 @@
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. 使用「匿名（不登录）」身份发起 POST 请求：/api/auth/login
-2. 请求体（application/json）：{   "username": "stu1789780379534",   "password": "123456" }
+2. 请求体（application/json）：{   "username": "stu1789785214233",   "password": "123456" }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40302，耗时 56 ms；断言 2/2 通过；返回信息：账号已被禁用，请联系管理员</t>
+          <t>HTTP 403，业务码 40302，耗时 57 ms；断言 2/2 通过；返回信息：账号已被禁用，请联系管理员</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 8 ms；断言 3/3 通过；返回信息：操作成功</t>
+          <t>HTTP 200，业务码 200，耗时 6 ms；断言 3/3 通过；返回信息：操作成功</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
@@ -9567,7 +9567,7 @@
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. 使用「非法 token」身份发起 POST 请求：/api/admin/categories
-2. 请求体（application/json）：{   "name": "接口测试分类-1789780395",   "sort": 88 }
+2. 请求体（application/json）：{   "name": "接口测试分类-1789785229",   "sort": 88 }
 3. 查看响应状态码、业务返回码与响应字段</t>
         </is>
       </c>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 16 ms；断言 3/3 通过；返回信息：分类新增成功</t>
+          <t>HTTP 200，业务码 200，耗时 13 ms；断言 3/3 通过；返回信息：分类新增成功</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400，业务码 40001，耗时 8 ms；断言 3/3 通过；返回信息：分类名称已存在</t>
+          <t>HTTP 400，业务码 40001，耗时 7 ms；断言 3/3 通过；返回信息：分类名称已存在</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409，业务码 40902，耗时 9 ms；断言 3/3 通过；返回信息：该分类下还有 8 件商品，无法删除</t>
+          <t>HTTP 409，业务码 40902，耗时 8 ms；断言 3/3 通过；返回信息：该分类下还有 8 件商品，无法删除</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 11 ms；断言 3/3 通过；返回信息：分类删除成功</t>
+          <t>HTTP 200，业务码 200，耗时 10 ms；断言 3/3 通过；返回信息：分类删除成功</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200，业务码 200，耗时 9 ms；断言 3/3 通过；返回信息：超时扫描完成</t>
+          <t>HTTP 200，业务码 200，耗时 6 ms；断言 3/3 通过；返回信息：超时扫描完成</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403，业务码 40303，耗时 7 ms；断言 2/2 通过；返回信息：需要管理员权限</t>
+          <t>HTTP 403，业务码 40303，耗时 5 ms；断言 2/2 通过；返回信息：需要管理员权限</t>
         </is>
       </c>
       <c r="J163" s="3" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>http://localhost:5173/login?redirect=/products/1；执行结果：通过</t>
+          <t>http://localhost:8080/login?redirect=/products/1；执行结果：通过</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-035629；执行结果：通过</t>
+          <t>前端联调测试商品-139105；执行结果：通过</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-035629；执行结果：通过</t>
+          <t>前端联调测试商品-139105；执行结果：通过</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>http://localhost:5173/products/21；执行结果：通过</t>
+          <t>http://localhost:8080/products/21；执行结果：通过</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>前端联调测试商品-035629；执行结果：通过</t>
+          <t>前端联调测试商品-139105；执行结果：通过</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>http://localhost:5173/orders?orderId=3；执行结果：通过</t>
+          <t>http://localhost:8080/orders?orderId=3；执行结果：通过</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>未读消息 1 条；执行结果：通过</t>
+          <t>未读消息 2 条；执行结果：通过</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>未读消息 1 条；执行结果：通过</t>
+          <t>未读消息 2 条；执行结果：通过</t>
         </is>
       </c>
       <c r="J218" s="3" t="inlineStr">
